--- a/artfynd/A 57876-2025 artfynd.xlsx
+++ b/artfynd/A 57876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404249</v>
       </c>
       <c r="B2" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404250</v>
       </c>
       <c r="B3" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57876-2025 artfynd.xlsx
+++ b/artfynd/A 57876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404249</v>
       </c>
       <c r="B2" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404250</v>
       </c>
       <c r="B3" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57876-2025 artfynd.xlsx
+++ b/artfynd/A 57876-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137404249</v>
       </c>
       <c r="B2" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137404250</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
